--- a/archives_mensuelles/2026-06_Juin.xlsx
+++ b/archives_mensuelles/2026-06_Juin.xlsx
@@ -732,7 +732,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>78,427 €</t>
+          <t>79,036 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -746,7 +746,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>87.1%</t>
+          <t>87.8%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -772,14 +772,14 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>29,800 €</t>
+          <t>29,966 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>48,627 €</t>
+          <t>49,070 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -912,7 +912,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>255</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -1466,8 +1466,8 @@
       <c r="N10" s="16" t="n">
         <v>353.5</v>
       </c>
-      <c r="O10" s="17" t="n">
-        <v>0</v>
+      <c r="O10" s="16" t="n">
+        <v>353.5</v>
       </c>
       <c r="P10" s="16" t="n">
         <v>0</v>
@@ -6507,10 +6507,10 @@
         <v>0</v>
       </c>
       <c r="O81" s="13" t="n">
-        <v>0</v>
+        <v>109.973</v>
       </c>
       <c r="P81" s="13" t="n">
-        <v>0</v>
+        <v>20.95</v>
       </c>
     </row>
     <row r="82">
@@ -6859,7 +6859,7 @@
         <v>360</v>
       </c>
       <c r="O86" s="17" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="P86" s="16" t="n">
         <v>0</v>
@@ -7363,10 +7363,10 @@
         <v>472.005</v>
       </c>
       <c r="O93" s="17" t="n">
-        <v>0</v>
+        <v>55.53</v>
       </c>
       <c r="P93" s="13" t="n">
-        <v>0</v>
+        <v>7.93</v>
       </c>
     </row>
     <row r="94">
@@ -14669,10 +14669,10 @@
         <v>57265.59</v>
       </c>
       <c r="O205" s="19" t="n">
-        <v>78426.94100000001</v>
+        <v>79035.944</v>
       </c>
       <c r="P205" s="19" t="n">
-        <v>151.55</v>
+        <v>152.73</v>
       </c>
     </row>
   </sheetData>
@@ -16205,10 +16205,10 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>385077</v>
+        <v>384468</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>181433</v>
+        <v>180824</v>
       </c>
       <c r="D5" s="25" t="n">
         <v>203645</v>
@@ -16230,10 +16230,10 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>189634</v>
+        <v>189469</v>
       </c>
       <c r="C6" s="26" t="n">
-        <v>85130</v>
+        <v>84964</v>
       </c>
       <c r="D6" s="26" t="n">
         <v>104505</v>
@@ -16255,10 +16255,10 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>195443</v>
+        <v>195000</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>96303</v>
+        <v>95859</v>
       </c>
       <c r="D7" s="27" t="n">
         <v>99140</v>

--- a/archives_mensuelles/2026-06_Juin.xlsx
+++ b/archives_mensuelles/2026-06_Juin.xlsx
@@ -732,7 +732,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>79,036 €</t>
+          <t>80,583 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -746,7 +746,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>87.8%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -772,14 +772,14 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>29,966 €</t>
+          <t>31,140 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>49,070 €</t>
+          <t>49,444 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -1891,10 +1891,10 @@
         <v>0</v>
       </c>
       <c r="O16" s="16" t="n">
-        <v>170</v>
+        <v>340</v>
       </c>
       <c r="P16" s="16" t="n">
-        <v>136</v>
+        <v>272</v>
       </c>
     </row>
     <row r="17">
@@ -2323,10 +2323,10 @@
         <v>0</v>
       </c>
       <c r="O22" s="16" t="n">
-        <v>1312.5</v>
+        <v>1837.5</v>
       </c>
       <c r="P22" s="16" t="n">
-        <v>1050</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="23">
@@ -2467,10 +2467,10 @@
         <v>0</v>
       </c>
       <c r="O24" s="16" t="n">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="P24" s="16" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25">
@@ -2747,10 +2747,10 @@
         <v>0</v>
       </c>
       <c r="O28" s="16" t="n">
-        <v>0</v>
+        <v>460</v>
       </c>
       <c r="P28" s="16" t="n">
-        <v>0</v>
+        <v>306.67</v>
       </c>
     </row>
     <row r="29">
@@ -3739,10 +3739,10 @@
         <v>203.5</v>
       </c>
       <c r="O42" s="16" t="n">
-        <v>203.5</v>
+        <v>407</v>
       </c>
       <c r="P42" s="16" t="n">
-        <v>116.29</v>
+        <v>232.57</v>
       </c>
     </row>
     <row r="43">
@@ -14669,10 +14669,10 @@
         <v>57265.59</v>
       </c>
       <c r="O205" s="19" t="n">
-        <v>79035.944</v>
+        <v>80583.444</v>
       </c>
       <c r="P205" s="19" t="n">
-        <v>152.73</v>
+        <v>155.72</v>
       </c>
     </row>
   </sheetData>
@@ -16205,16 +16205,16 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>384468</v>
+        <v>395307</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>180824</v>
+        <v>191866</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>203645</v>
+        <v>203441</v>
       </c>
       <c r="E5" s="25" t="n">
-        <v>172285</v>
+        <v>172082</v>
       </c>
       <c r="F5" s="25" t="n">
         <v>15760</v>
@@ -16230,10 +16230,10 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>189469</v>
+        <v>188295</v>
       </c>
       <c r="C6" s="26" t="n">
-        <v>84964</v>
+        <v>83790</v>
       </c>
       <c r="D6" s="26" t="n">
         <v>104505</v>
@@ -16255,16 +16255,16 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>195000</v>
+        <v>207012</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>95859</v>
+        <v>108075</v>
       </c>
       <c r="D7" s="27" t="n">
-        <v>99140</v>
+        <v>98937</v>
       </c>
       <c r="E7" s="27" t="n">
-        <v>75289</v>
+        <v>75086</v>
       </c>
       <c r="F7" s="27" t="n">
         <v>12700</v>
@@ -16284,7 +16284,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -16308,7 +16308,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 37 commande(s)</t>
+          <t>Épics créées ce mois — 38 commande(s)</t>
         </is>
       </c>
     </row>
@@ -16363,22 +16363,22 @@
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34345</t>
+          <t>PDMDEP-34380</t>
         </is>
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34337</t>
+          <t>PDMDEP-34287</t>
         </is>
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="D5" s="15" t="inlineStr">
         <is>
-          <t>Commune de Chalons-sur-Saone</t>
+          <t>COMMUNE DE LUNEL</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -16388,19 +16388,11 @@
       </c>
       <c r="F5" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
-      <c r="G5" s="15" t="inlineStr">
-        <is>
-          <t>Services</t>
-        </is>
-      </c>
-      <c r="H5" s="15" t="inlineStr">
-        <is>
-          <t>00171711</t>
-        </is>
-      </c>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="G5" s="15" t="inlineStr"/>
+      <c r="H5" s="15" t="inlineStr"/>
       <c r="I5" s="26" t="n">
         <v>0</v>
       </c>
@@ -17038,22 +17030,22 @@
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34326</t>
+          <t>PDMDEP-34117</t>
         </is>
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34319</t>
+          <t>PDMDEP-34108</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>Commune de Mouscron (BE)</t>
+          <t>COMMUNE DU PUY EN VELAY</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
@@ -17073,22 +17065,22 @@
       </c>
       <c r="H20" s="12" t="inlineStr">
         <is>
-          <t>00171691</t>
+          <t>00170907</t>
         </is>
       </c>
       <c r="I20" s="27" t="n">
-        <v>0</v>
+        <v>3535</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34310</t>
+          <t>PDMDEP-34345</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34303</t>
+          <t>PDMDEP-34337</t>
         </is>
       </c>
       <c r="C21" s="15" t="inlineStr">
@@ -17098,7 +17090,7 @@
       </c>
       <c r="D21" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE GAP</t>
+          <t>Commune de Chalons-sur-Saone</t>
         </is>
       </c>
       <c r="E21" s="15" t="inlineStr">
@@ -17108,7 +17100,7 @@
       </c>
       <c r="F21" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G21" s="15" t="inlineStr">
@@ -17118,7 +17110,7 @@
       </c>
       <c r="H21" s="15" t="inlineStr">
         <is>
-          <t>00171605</t>
+          <t>00171711</t>
         </is>
       </c>
       <c r="I21" s="26" t="n">
@@ -17128,22 +17120,22 @@
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34258</t>
+          <t>PDMDEP-34155</t>
         </is>
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34249</t>
+          <t>PDMDEP-34147</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE VIENNE</t>
+          <t>Mairie de Vaison la romaine</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr">
@@ -17153,7 +17145,7 @@
       </c>
       <c r="F22" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G22" s="12" t="inlineStr">
@@ -17163,32 +17155,32 @@
       </c>
       <c r="H22" s="12" t="inlineStr">
         <is>
-          <t>00171361</t>
+          <t>00171080</t>
         </is>
       </c>
       <c r="I22" s="27" t="n">
-        <v>0</v>
+        <v>1414.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34227</t>
+          <t>PDMDEP-34326</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34169</t>
+          <t>PDMDEP-34319</t>
         </is>
       </c>
       <c r="C23" s="15" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="D23" s="15" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
+          <t>Commune de Mouscron (BE)</t>
         </is>
       </c>
       <c r="E23" s="15" t="inlineStr">
@@ -17201,35 +17193,39 @@
           <t>Migration</t>
         </is>
       </c>
-      <c r="G23" s="15" t="inlineStr"/>
+      <c r="G23" s="15" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
       <c r="H23" s="15" t="inlineStr">
         <is>
-          <t>2026-0210095</t>
+          <t>00171691</t>
         </is>
       </c>
       <c r="I23" s="26" t="n">
-        <v>32077</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34070</t>
+          <t>PDMDEP-34310</t>
         </is>
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34064</t>
+          <t>PDMDEP-34303</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE VANNES</t>
+          <t>COMMUNE DE GAP</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
@@ -17239,7 +17235,7 @@
       </c>
       <c r="F24" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G24" s="12" t="inlineStr">
@@ -17249,22 +17245,22 @@
       </c>
       <c r="H24" s="12" t="inlineStr">
         <is>
-          <t>00170468</t>
+          <t>00171605</t>
         </is>
       </c>
       <c r="I24" s="27" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34216</t>
+          <t>PDMDEP-34201</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34208</t>
+          <t>PDMDEP-34192</t>
         </is>
       </c>
       <c r="C25" s="15" t="inlineStr">
@@ -17274,7 +17270,7 @@
       </c>
       <c r="D25" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHATEAUGIRON</t>
+          <t xml:space="preserve">Commune de Macon </t>
         </is>
       </c>
       <c r="E25" s="15" t="inlineStr">
@@ -17284,7 +17280,7 @@
       </c>
       <c r="F25" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="G25" s="15" t="inlineStr">
@@ -17294,7 +17290,7 @@
       </c>
       <c r="H25" s="15" t="inlineStr">
         <is>
-          <t>00171155</t>
+          <t>00171162</t>
         </is>
       </c>
       <c r="I25" s="26" t="n">
@@ -17304,22 +17300,22 @@
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34155</t>
+          <t>PDMDEP-34216</t>
         </is>
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34147</t>
+          <t>PDMDEP-34208</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>Mairie de Vaison la romaine</t>
+          <t>COMMUNE DE CHATEAUGIRON</t>
         </is>
       </c>
       <c r="E26" s="12" t="inlineStr">
@@ -17329,7 +17325,7 @@
       </c>
       <c r="F26" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G26" s="12" t="inlineStr">
@@ -17339,32 +17335,32 @@
       </c>
       <c r="H26" s="12" t="inlineStr">
         <is>
-          <t>00171080</t>
+          <t>00171155</t>
         </is>
       </c>
       <c r="I26" s="27" t="n">
-        <v>1414.5</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34117</t>
+          <t>PDMDEP-34258</t>
         </is>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34108</t>
+          <t>PDMDEP-34249</t>
         </is>
       </c>
       <c r="C27" s="15" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="D27" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DU PUY EN VELAY</t>
+          <t>COMMUNE DE VIENNE</t>
         </is>
       </c>
       <c r="E27" s="15" t="inlineStr">
@@ -17384,32 +17380,32 @@
       </c>
       <c r="H27" s="15" t="inlineStr">
         <is>
-          <t>00170907</t>
+          <t>00171361</t>
         </is>
       </c>
       <c r="I27" s="26" t="n">
-        <v>3535</v>
+        <v>10636</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34201</t>
+          <t>PDMDEP-34070</t>
         </is>
       </c>
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34192</t>
+          <t>PDMDEP-34064</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commune de Macon </t>
+          <t>VILLE DE VANNES</t>
         </is>
       </c>
       <c r="E28" s="12" t="inlineStr">
@@ -17419,7 +17415,7 @@
       </c>
       <c r="F28" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G28" s="12" t="inlineStr">
@@ -17429,73 +17425,73 @@
       </c>
       <c r="H28" s="12" t="inlineStr">
         <is>
-          <t>00171162</t>
+          <t>00170468</t>
         </is>
       </c>
       <c r="I28" s="27" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33833</t>
+          <t>PDMDEP-34227</t>
         </is>
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33822</t>
+          <t>PDMDEP-34169</t>
         </is>
       </c>
       <c r="C29" s="15" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="D29" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU FINISTERE (CD 29)</t>
+          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
         </is>
       </c>
       <c r="E29" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="F29" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G29" s="15" t="inlineStr"/>
       <c r="H29" s="15" t="inlineStr">
         <is>
-          <t>00169872</t>
+          <t>2026-0210095</t>
         </is>
       </c>
       <c r="I29" s="26" t="n">
-        <v>2625</v>
+        <v>32077</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33817</t>
+          <t>PDMDEP-34235</t>
         </is>
       </c>
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33813</t>
+          <t>PDMDEP-34229</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>DIJON METROPOLE</t>
         </is>
       </c>
       <c r="E30" s="12" t="inlineStr">
@@ -17515,32 +17511,32 @@
       </c>
       <c r="H30" s="12" t="inlineStr">
         <is>
-          <t>00169865</t>
+          <t>00171333</t>
         </is>
       </c>
       <c r="I30" s="27" t="n">
-        <v>1095.5</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33808</t>
+          <t>PDMDEP-33703</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33804</t>
+          <t>PDMDEP-33699</t>
         </is>
       </c>
       <c r="C31" s="15" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="D31" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
+          <t>DEPARTEMENT D'ILLE ET VILAINE (CD 35)</t>
         </is>
       </c>
       <c r="E31" s="15" t="inlineStr">
@@ -17560,32 +17556,32 @@
       </c>
       <c r="H31" s="15" t="inlineStr">
         <is>
-          <t>00169856</t>
+          <t>00169363</t>
         </is>
       </c>
       <c r="I31" s="26" t="n">
-        <v>1890</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33794</t>
+          <t>PDMDEP-33724</t>
         </is>
       </c>
       <c r="B32" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33790</t>
+          <t>PDMDEP-33720</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E32" s="12" t="inlineStr">
@@ -17605,32 +17601,32 @@
       </c>
       <c r="H32" s="12" t="inlineStr">
         <is>
-          <t>00169697</t>
+          <t>00169462</t>
         </is>
       </c>
       <c r="I32" s="27" t="n">
-        <v>6655</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33745</t>
+          <t>PDMDEP-33794</t>
         </is>
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33739</t>
+          <t>PDMDEP-33790</t>
         </is>
       </c>
       <c r="C33" s="15" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="D33" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
         </is>
       </c>
       <c r="E33" s="15" t="inlineStr">
@@ -17650,22 +17646,22 @@
       </c>
       <c r="H33" s="15" t="inlineStr">
         <is>
-          <t>00169509</t>
+          <t>00169697</t>
         </is>
       </c>
       <c r="I33" s="26" t="n">
-        <v>2300</v>
+        <v>6655</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33733</t>
+          <t>PDMDEP-33745</t>
         </is>
       </c>
       <c r="B34" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33729</t>
+          <t>PDMDEP-33739</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
@@ -17675,7 +17671,7 @@
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information</t>
+          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
         </is>
       </c>
       <c r="E34" s="12" t="inlineStr">
@@ -17695,32 +17691,32 @@
       </c>
       <c r="H34" s="12" t="inlineStr">
         <is>
-          <t>00169480</t>
+          <t>00169509</t>
         </is>
       </c>
       <c r="I34" s="27" t="n">
-        <v>755</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33724</t>
+          <t>PDMDEP-33808</t>
         </is>
       </c>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33720</t>
+          <t>PDMDEP-33804</t>
         </is>
       </c>
       <c r="C35" s="15" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="D35" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
         </is>
       </c>
       <c r="E35" s="15" t="inlineStr">
@@ -17740,32 +17736,32 @@
       </c>
       <c r="H35" s="15" t="inlineStr">
         <is>
-          <t>00169462</t>
+          <t>00169856</t>
         </is>
       </c>
       <c r="I35" s="26" t="n">
-        <v>1000</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33703</t>
+          <t>PDMDEP-33817</t>
         </is>
       </c>
       <c r="B36" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33699</t>
+          <t>PDMDEP-33813</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>DEPARTEMENT D'ILLE ET VILAINE (CD 35)</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E36" s="12" t="inlineStr">
@@ -17785,32 +17781,32 @@
       </c>
       <c r="H36" s="12" t="inlineStr">
         <is>
-          <t>00169363</t>
+          <t>00169865</t>
         </is>
       </c>
       <c r="I36" s="27" t="n">
-        <v>1350</v>
+        <v>1095.5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33570</t>
+          <t>PDMDEP-33833</t>
         </is>
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33566</t>
+          <t>PDMDEP-33822</t>
         </is>
       </c>
       <c r="C37" s="15" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="D37" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE LILLE</t>
+          <t>DEPARTEMENT DU FINISTERE (CD 29)</t>
         </is>
       </c>
       <c r="E37" s="15" t="inlineStr">
@@ -17823,39 +17819,35 @@
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G37" s="15" t="inlineStr">
-        <is>
-          <t>Services</t>
-        </is>
-      </c>
+      <c r="G37" s="15" t="inlineStr"/>
       <c r="H37" s="15" t="inlineStr">
         <is>
-          <t>00168466</t>
+          <t>00169872</t>
         </is>
       </c>
       <c r="I37" s="26" t="n">
-        <v>895</v>
+        <v>2625</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34235</t>
+          <t>PDMDEP-33944</t>
         </is>
       </c>
       <c r="B38" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34229</t>
+          <t>PDMDEP-33940</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>DIJON METROPOLE</t>
+          <t>Commune de Thionville</t>
         </is>
       </c>
       <c r="E38" s="12" t="inlineStr">
@@ -17875,32 +17867,32 @@
       </c>
       <c r="H38" s="12" t="inlineStr">
         <is>
-          <t>00171333</t>
+          <t>00170299</t>
         </is>
       </c>
       <c r="I38" s="27" t="n">
-        <v>7200</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33955</t>
+          <t>PDMDEP-33570</t>
         </is>
       </c>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33949</t>
+          <t>PDMDEP-33566</t>
         </is>
       </c>
       <c r="C39" s="15" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="D39" s="15" t="inlineStr">
         <is>
-          <t>Commune de Colmar</t>
+          <t>COMMUNE DE LILLE</t>
         </is>
       </c>
       <c r="E39" s="15" t="inlineStr">
@@ -17920,11 +17912,11 @@
       </c>
       <c r="H39" s="15" t="inlineStr">
         <is>
-          <t>00170302</t>
+          <t>00168466</t>
         </is>
       </c>
       <c r="I39" s="26" t="n">
-        <v>12429</v>
+        <v>895</v>
       </c>
     </row>
     <row r="40">
@@ -17975,73 +17967,97 @@
     <row r="41">
       <c r="A41" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33944</t>
+          <t>PDMDEP-33733</t>
         </is>
       </c>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33940</t>
+          <t>PDMDEP-33729</t>
         </is>
       </c>
       <c r="C41" s="15" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="D41" s="15" t="inlineStr">
+        <is>
+          <t>VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information</t>
+        </is>
+      </c>
+      <c r="E41" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F41" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G41" s="15" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H41" s="15" t="inlineStr">
+        <is>
+          <t>00169480</t>
+        </is>
+      </c>
+      <c r="I41" s="26" t="n">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-33955</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-33949</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="D41" s="15" t="inlineStr">
-        <is>
-          <t>Commune de Thionville</t>
-        </is>
-      </c>
-      <c r="E41" s="15" t="inlineStr">
+      <c r="D42" s="12" t="inlineStr">
+        <is>
+          <t>Commune de Colmar</t>
+        </is>
+      </c>
+      <c r="E42" s="12" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="F41" s="15" t="inlineStr">
+      <c r="F42" s="12" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G41" s="15" t="inlineStr">
+      <c r="G42" s="12" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="H41" s="15" t="inlineStr">
-        <is>
-          <t>00170299</t>
-        </is>
-      </c>
-      <c r="I41" s="26" t="n">
-        <v>2200</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="18" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B42" s="18" t="n"/>
-      <c r="C42" s="18" t="n"/>
-      <c r="D42" s="18" t="n"/>
-      <c r="E42" s="18" t="n"/>
-      <c r="F42" s="18" t="n"/>
-      <c r="G42" s="18" t="n"/>
-      <c r="H42" s="18" t="inlineStr">
-        <is>
-          <t>37 commande(s)</t>
-        </is>
-      </c>
-      <c r="I42" s="25" t="n">
-        <v>118111</v>
+      <c r="H42" s="12" t="inlineStr">
+        <is>
+          <t>00170302</t>
+        </is>
+      </c>
+      <c r="I42" s="27" t="n">
+        <v>12429</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="18" t="inlineStr">
         <is>
-          <t>dont Littéralis</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B43" s="18" t="n"/>
@@ -18052,17 +18068,17 @@
       <c r="G43" s="18" t="n"/>
       <c r="H43" s="18" t="inlineStr">
         <is>
-          <t>13 commande(s)</t>
+          <t>38 commande(s)</t>
         </is>
       </c>
       <c r="I43" s="25" t="n">
-        <v>42234</v>
+        <v>130497</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="18" t="inlineStr">
         <is>
-          <t>dont GEODP</t>
+          <t>dont Littéralis</t>
         </is>
       </c>
       <c r="B44" s="18" t="n"/>
@@ -18073,11 +18089,32 @@
       <c r="G44" s="18" t="n"/>
       <c r="H44" s="18" t="inlineStr">
         <is>
-          <t>24 commande(s)</t>
+          <t>13 commande(s)</t>
         </is>
       </c>
       <c r="I44" s="25" t="n">
-        <v>75876</v>
+        <v>42234</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="18" t="inlineStr">
+        <is>
+          <t>dont GEODP</t>
+        </is>
+      </c>
+      <c r="B45" s="18" t="n"/>
+      <c r="C45" s="18" t="n"/>
+      <c r="D45" s="18" t="n"/>
+      <c r="E45" s="18" t="n"/>
+      <c r="F45" s="18" t="n"/>
+      <c r="G45" s="18" t="n"/>
+      <c r="H45" s="18" t="inlineStr">
+        <is>
+          <t>25 commande(s)</t>
+        </is>
+      </c>
+      <c r="I45" s="25" t="n">
+        <v>88262</v>
       </c>
     </row>
   </sheetData>

--- a/archives_mensuelles/2026-06_Juin.xlsx
+++ b/archives_mensuelles/2026-06_Juin.xlsx
@@ -732,7 +732,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>80,583 €</t>
+          <t>81,371 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -746,7 +746,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -772,14 +772,14 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>31,140 €</t>
+          <t>31,324 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>49,444 €</t>
+          <t>50,047 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -4795,10 +4795,10 @@
         <v>184.5</v>
       </c>
       <c r="O57" s="13" t="n">
-        <v>332.1</v>
+        <v>516.6</v>
       </c>
       <c r="P57" s="13" t="n">
-        <v>1328.4</v>
+        <v>2066.4</v>
       </c>
     </row>
     <row r="58">
@@ -4939,7 +4939,7 @@
         <v>603.5</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>603.5</v>
+        <v>1207</v>
       </c>
       <c r="P59" s="13" t="n">
         <v>0</v>
@@ -14669,10 +14669,10 @@
         <v>57265.59</v>
       </c>
       <c r="O205" s="19" t="n">
-        <v>80583.444</v>
+        <v>81371.444</v>
       </c>
       <c r="P205" s="19" t="n">
-        <v>155.72</v>
+        <v>157.24</v>
       </c>
     </row>
   </sheetData>
@@ -16205,16 +16205,16 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>395307</v>
+        <v>394519</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>191866</v>
+        <v>191681</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>203441</v>
+        <v>202838</v>
       </c>
       <c r="E5" s="25" t="n">
-        <v>172082</v>
+        <v>171478</v>
       </c>
       <c r="F5" s="25" t="n">
         <v>15760</v>
@@ -16230,10 +16230,10 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>188295</v>
+        <v>188110</v>
       </c>
       <c r="C6" s="26" t="n">
-        <v>83790</v>
+        <v>83606</v>
       </c>
       <c r="D6" s="26" t="n">
         <v>104505</v>
@@ -16255,16 +16255,16 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>207012</v>
+        <v>206409</v>
       </c>
       <c r="C7" s="27" t="n">
         <v>108075</v>
       </c>
       <c r="D7" s="27" t="n">
-        <v>98937</v>
+        <v>98333</v>
       </c>
       <c r="E7" s="27" t="n">
-        <v>75086</v>
+        <v>74482</v>
       </c>
       <c r="F7" s="27" t="n">
         <v>12700</v>
